--- a/2026_DSAIML_Club_Batch/01 Advanced Excel/2026_03_12.xlsx
+++ b/2026_DSAIML_Club_Batch/01 Advanced Excel/2026_03_12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\all_batches\2026_DSAIML_Club_Batch\01 Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F252498B-2BE9-49E5-9FEA-280A8774D9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFD76483-11C9-4AA3-8E89-42CB1FE884AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="flashfill and concat" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="79">
   <si>
     <t>First Name</t>
   </si>
@@ -257,13 +257,19 @@
   </si>
   <si>
     <t>Krushnam</t>
+  </si>
+  <si>
+    <t>Type your Initial</t>
+  </si>
+  <si>
+    <t>NAND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +281,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -362,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -377,6 +396,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1048,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBB6FE8-5F03-48CA-B413-558FA0DB4599}">
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -1069,9 +1091,10 @@
     <col min="18" max="18" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -1079,7 +1102,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1096,7 +1119,7 @@
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -1111,7 +1134,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1123,156 +1146,993 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:22" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="O5" t="s">
+      <c r="O5" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="S5" t="s">
+      <c r="S5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="T5" t="s">
+      <c r="T5" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="U5" t="s">
+      <c r="U5" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>38036</v>
       </c>
       <c r="B6">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <f>YEAR(A6)</f>
+        <v>2004</v>
+      </c>
+      <c r="D6">
+        <f>DAY(A6)</f>
+        <v>19</v>
+      </c>
+      <c r="E6">
+        <f>MONTH(A6)</f>
+        <v>2</v>
+      </c>
+      <c r="F6" t="b">
+        <f>AND(B6&gt;=10, E6=4)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" t="b">
+        <f>OR(E6=4, B6&gt;=10)</f>
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <f>NOT(E6=4)</f>
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
+        <f>TEXT(A6, "yyyy")</f>
+        <v>2004</v>
+      </c>
+      <c r="J6" t="str">
+        <f>TEXT(A6, "yy")</f>
+        <v>04</v>
+      </c>
+      <c r="K6" t="str">
+        <f>TEXT(A6, "m")</f>
+        <v>2</v>
+      </c>
+      <c r="L6" t="str">
+        <f>TEXT(A6, "mm")</f>
+        <v>02</v>
+      </c>
+      <c r="M6" t="str">
+        <f>TEXT(A6, "mmm")</f>
+        <v>Feb</v>
+      </c>
+      <c r="N6" t="str">
+        <f>TEXT(A6, "mmmm")</f>
+        <v>February</v>
+      </c>
+      <c r="O6" t="str">
+        <f>TEXT(A6, "d")</f>
+        <v>19</v>
+      </c>
+      <c r="P6" t="str">
+        <f>TEXT(A6, "dd")</f>
+        <v>19</v>
+      </c>
+      <c r="Q6" t="str">
+        <f>TEXT(A6, "ddd")</f>
+        <v>Thu</v>
+      </c>
+      <c r="R6" t="str">
+        <f>TEXT(A6, "dddd")</f>
+        <v>Thursday</v>
+      </c>
+      <c r="S6" t="str">
+        <f>TEXT(B6, "00")</f>
+        <v>33</v>
+      </c>
+      <c r="T6" t="str">
+        <f>TEXT(B6, "000")</f>
+        <v>033</v>
+      </c>
+      <c r="U6">
+        <f>_xlfn.NUMBERVALUE(T6)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>39091</v>
       </c>
       <c r="B7">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <f t="shared" ref="C7:C20" si="0">YEAR(A7)</f>
+        <v>2007</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:D20" si="1">DAY(A7)</f>
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ref="E7:E20" si="2">MONTH(A7)</f>
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <f t="shared" ref="F7:F20" si="3">AND(B7&gt;=10, E7=4)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <f t="shared" ref="G7:G20" si="4">OR(E7=4, B7&gt;=10)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <f t="shared" ref="H7:H20" si="5">NOT(E7=4)</f>
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" ref="I7:I20" si="6">TEXT(A7, "yyyy")</f>
+        <v>2007</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" ref="J7:J20" si="7">TEXT(A7, "yy")</f>
+        <v>07</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" ref="K7:K20" si="8">TEXT(A7, "m")</f>
+        <v>1</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" ref="L7:L20" si="9">TEXT(A7, "mm")</f>
+        <v>01</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" ref="M7:M20" si="10">TEXT(A7, "mmm")</f>
+        <v>Jan</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" ref="N7:N20" si="11">TEXT(A7, "mmmm")</f>
+        <v>January</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" ref="O7:O20" si="12">TEXT(A7, "d")</f>
+        <v>9</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" ref="P7:P20" si="13">TEXT(A7, "dd")</f>
+        <v>09</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" ref="Q7:Q20" si="14">TEXT(A7, "ddd")</f>
+        <v>Tue</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" ref="R7:R20" si="15">TEXT(A7, "dddd")</f>
+        <v>Tuesday</v>
+      </c>
+      <c r="S7" t="str">
+        <f t="shared" ref="S7:S20" si="16">TEXT(B7, "00")</f>
+        <v>09</v>
+      </c>
+      <c r="T7" t="str">
+        <f t="shared" ref="T7:T20" si="17">TEXT(B7, "000")</f>
+        <v>009</v>
+      </c>
+      <c r="U7">
+        <f t="shared" ref="U7:U20" si="18">_xlfn.NUMBERVALUE(T7)</f>
+        <v>9</v>
+      </c>
+      <c r="V7" s="12"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>39558</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F8" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="9"/>
+        <v>04</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="10"/>
+        <v>Apr</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="11"/>
+        <v>April</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="14"/>
+        <v>Sun</v>
+      </c>
+      <c r="R8" t="str">
+        <f t="shared" si="15"/>
+        <v>Sunday</v>
+      </c>
+      <c r="S8" t="str">
+        <f t="shared" si="16"/>
+        <v>05</v>
+      </c>
+      <c r="T8" t="str">
+        <f t="shared" si="17"/>
+        <v>005</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>40288</v>
       </c>
       <c r="B9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>2010</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F9" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G9" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="6"/>
+        <v>2010</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="9"/>
+        <v>04</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="10"/>
+        <v>Apr</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="11"/>
+        <v>April</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="14"/>
+        <v>Tue</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="15"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="S9" t="str">
+        <f t="shared" si="16"/>
+        <v>05</v>
+      </c>
+      <c r="T9" t="str">
+        <f t="shared" si="17"/>
+        <v>005</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>39924</v>
       </c>
       <c r="B10">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>2009</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F10" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G10" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="6"/>
+        <v>2009</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="7"/>
+        <v>09</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="9"/>
+        <v>04</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="10"/>
+        <v>Apr</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="11"/>
+        <v>April</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="12"/>
+        <v>21</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="14"/>
+        <v>Tue</v>
+      </c>
+      <c r="R10" t="str">
+        <f t="shared" si="15"/>
+        <v>Tuesday</v>
+      </c>
+      <c r="S10" t="str">
+        <f t="shared" si="16"/>
+        <v>06</v>
+      </c>
+      <c r="T10" t="str">
+        <f t="shared" si="17"/>
+        <v>006</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>38829</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>2006</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F11" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G11" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="6"/>
+        <v>2006</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="7"/>
+        <v>06</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="9"/>
+        <v>04</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="10"/>
+        <v>Apr</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="11"/>
+        <v>April</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="13"/>
+        <v>22</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="14"/>
+        <v>Sat</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="15"/>
+        <v>Saturday</v>
+      </c>
+      <c r="S11" t="str">
+        <f t="shared" si="16"/>
+        <v>09</v>
+      </c>
+      <c r="T11" t="str">
+        <f t="shared" si="17"/>
+        <v>009</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>39561</v>
       </c>
       <c r="B12">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F12" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G12" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="9"/>
+        <v>04</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" si="10"/>
+        <v>Apr</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="11"/>
+        <v>April</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="14"/>
+        <v>Wed</v>
+      </c>
+      <c r="R12" t="str">
+        <f t="shared" si="15"/>
+        <v>Wednesday</v>
+      </c>
+      <c r="S12" t="str">
+        <f t="shared" si="16"/>
+        <v>06</v>
+      </c>
+      <c r="T12" t="str">
+        <f t="shared" si="17"/>
+        <v>006</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="18"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>42148</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>2015</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F13" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G13" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="6"/>
+        <v>2015</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="9"/>
+        <v>05</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" si="10"/>
+        <v>May</v>
+      </c>
+      <c r="N13" t="str">
+        <f t="shared" si="11"/>
+        <v>May</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="14"/>
+        <v>Sun</v>
+      </c>
+      <c r="R13" t="str">
+        <f t="shared" si="15"/>
+        <v>Sunday</v>
+      </c>
+      <c r="S13" t="str">
+        <f t="shared" si="16"/>
+        <v>03</v>
+      </c>
+      <c r="T13" t="str">
+        <f t="shared" si="17"/>
+        <v>003</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="18"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>39807</v>
       </c>
       <c r="B14">
         <v>66</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="F14" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G14" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="9"/>
+        <v>12</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" si="10"/>
+        <v>Dec</v>
+      </c>
+      <c r="N14" t="str">
+        <f t="shared" si="11"/>
+        <v>December</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="14"/>
+        <v>Thu</v>
+      </c>
+      <c r="R14" t="str">
+        <f t="shared" si="15"/>
+        <v>Thursday</v>
+      </c>
+      <c r="S14" t="str">
+        <f t="shared" si="16"/>
+        <v>66</v>
+      </c>
+      <c r="T14" t="str">
+        <f t="shared" si="17"/>
+        <v>066</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="18"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>39655</v>
       </c>
       <c r="B15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F15" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G15" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="8"/>
+        <v>7</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="9"/>
+        <v>07</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="10"/>
+        <v>Jul</v>
+      </c>
+      <c r="N15" t="str">
+        <f t="shared" si="11"/>
+        <v>July</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="14"/>
+        <v>Sat</v>
+      </c>
+      <c r="R15" t="str">
+        <f t="shared" si="15"/>
+        <v>Saturday</v>
+      </c>
+      <c r="S15" t="str">
+        <f t="shared" si="16"/>
+        <v>07</v>
+      </c>
+      <c r="T15" t="str">
+        <f t="shared" si="17"/>
+        <v>007</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="18"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>39564</v>
       </c>
       <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F16" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="9"/>
+        <v>04</v>
+      </c>
+      <c r="M16" t="str">
+        <f t="shared" si="10"/>
+        <v>Apr</v>
+      </c>
+      <c r="N16" t="str">
+        <f t="shared" si="11"/>
+        <v>April</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="12"/>
+        <v>26</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="13"/>
+        <v>26</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="14"/>
+        <v>Sat</v>
+      </c>
+      <c r="R16" t="str">
+        <f t="shared" si="15"/>
+        <v>Saturday</v>
+      </c>
+      <c r="S16" t="str">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+      <c r="T16" t="str">
+        <f t="shared" si="17"/>
+        <v>015</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="18"/>
         <v>15</v>
       </c>
     </row>
@@ -1283,6 +2143,82 @@
       <c r="B17">
         <v>10</v>
       </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="F17" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G17" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="8"/>
+        <v>12</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="9"/>
+        <v>12</v>
+      </c>
+      <c r="M17" t="str">
+        <f t="shared" si="10"/>
+        <v>Dec</v>
+      </c>
+      <c r="N17" t="str">
+        <f t="shared" si="11"/>
+        <v>December</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="13"/>
+        <v>27</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="14"/>
+        <v>Sat</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="15"/>
+        <v>Saturday</v>
+      </c>
+      <c r="S17" t="str">
+        <f t="shared" si="16"/>
+        <v>10</v>
+      </c>
+      <c r="T17" t="str">
+        <f t="shared" si="17"/>
+        <v>010</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="18"/>
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
@@ -1291,6 +2227,82 @@
       <c r="B18">
         <v>4</v>
       </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F18" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G18" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H18" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="8"/>
+        <v>9</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="9"/>
+        <v>09</v>
+      </c>
+      <c r="M18" t="str">
+        <f t="shared" si="10"/>
+        <v>Sep</v>
+      </c>
+      <c r="N18" t="str">
+        <f t="shared" si="11"/>
+        <v>September</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="12"/>
+        <v>27</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="13"/>
+        <v>27</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="14"/>
+        <v>Sat</v>
+      </c>
+      <c r="R18" t="str">
+        <f t="shared" si="15"/>
+        <v>Saturday</v>
+      </c>
+      <c r="S18" t="str">
+        <f t="shared" si="16"/>
+        <v>04</v>
+      </c>
+      <c r="T18" t="str">
+        <f t="shared" si="17"/>
+        <v>004</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="18"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
@@ -1299,12 +2311,164 @@
       <c r="B19">
         <v>13</v>
       </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F19" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G19" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="9"/>
+        <v>08</v>
+      </c>
+      <c r="M19" t="str">
+        <f t="shared" si="10"/>
+        <v>Aug</v>
+      </c>
+      <c r="N19" t="str">
+        <f t="shared" si="11"/>
+        <v>August</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="12"/>
+        <v>28</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="13"/>
+        <v>28</v>
+      </c>
+      <c r="Q19" t="str">
+        <f t="shared" si="14"/>
+        <v>Thu</v>
+      </c>
+      <c r="R19" t="str">
+        <f t="shared" si="15"/>
+        <v>Thursday</v>
+      </c>
+      <c r="S19" t="str">
+        <f t="shared" si="16"/>
+        <v>13</v>
+      </c>
+      <c r="T19" t="str">
+        <f t="shared" si="17"/>
+        <v>013</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="18"/>
+        <v>13</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>39507</v>
       </c>
       <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>2008</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F20" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G20" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="6"/>
+        <v>2008</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="7"/>
+        <v>08</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="9"/>
+        <v>02</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="shared" si="10"/>
+        <v>Feb</v>
+      </c>
+      <c r="N20" t="str">
+        <f t="shared" si="11"/>
+        <v>February</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="12"/>
+        <v>29</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="13"/>
+        <v>29</v>
+      </c>
+      <c r="Q20" t="str">
+        <f t="shared" si="14"/>
+        <v>Fri</v>
+      </c>
+      <c r="R20" t="str">
+        <f t="shared" si="15"/>
+        <v>Friday</v>
+      </c>
+      <c r="S20" t="str">
+        <f t="shared" si="16"/>
+        <v>07</v>
+      </c>
+      <c r="T20" t="str">
+        <f t="shared" si="17"/>
+        <v>007</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="18"/>
         <v>7</v>
       </c>
     </row>
@@ -1319,7 +2483,7 @@
       </c>
       <c r="U22">
         <f>SUM(U6:U20)</f>
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
@@ -1327,24 +2491,31 @@
         <v>63</v>
       </c>
       <c r="C23" s="6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
         <v>64</v>
       </c>
       <c r="S23">
         <f>S6+S7+S8+S9</f>
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C24" s="5"/>
+      <c r="C24" s="5" t="b">
+        <f>AND(C23&gt;=30, C23&lt;=40)</f>
+        <v>1</v>
+      </c>
       <c r="E24" s="2">
-        <f>DATE(2026,1,18)</f>
-        <v>46040</v>
+        <f>DATE(2006, 9, 17)</f>
+        <v>38977</v>
+      </c>
+      <c r="F24" t="str">
+        <f>TEXT(E24, "dddd")</f>
+        <v>Sunday</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1352,23 +2523,33 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
         <v>66</v>
+      </c>
+      <c r="F26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="5"/>
+      <c r="C27" s="5" t="str">
+        <f>IF(OR(C26="Dr", C26="Prof"), "Yes", "No")</f>
+        <v>Yes</v>
+      </c>
       <c r="E27" s="4">
         <f ca="1">NOW()</f>
-        <v>46093.788544444447</v>
+        <v>46099.745055439816</v>
+      </c>
+      <c r="F27">
+        <f ca="1">YEAR(E27)</f>
+        <v>2026</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
@@ -1377,14 +2558,17 @@
         <v>69</v>
       </c>
       <c r="C29" s="6">
-        <v>2004</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="5"/>
+      <c r="C30" s="5" t="str">
+        <f>IF(C29=2006, "Yes", "No")</f>
+        <v>No</v>
+      </c>
     </row>
     <row r="31" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
@@ -1395,11 +2579,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C33" s="5"/>
+      <c r="C33" s="5" t="b">
+        <f>NOT(AND(C32&gt;=30, C32&lt;=40))</f>
+        <v>0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>78</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
